--- a/backend/data/financials_by_company/1833.SR.xlsx
+++ b/backend/data/financials_by_company/1833.SR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,195 +657,105 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>215175.36792</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.08994000000000001</v>
-      </c>
-      <c r="D2" t="n">
-        <v>130903517</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2392429</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2392429</v>
-      </c>
-      <c r="G2" t="n">
-        <v>95423397</v>
-      </c>
-      <c r="H2" t="n">
-        <v>22491883</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1842894967</v>
-      </c>
-      <c r="J2" t="n">
-        <v>133295946</v>
-      </c>
-      <c r="K2" t="n">
-        <v>110804063</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-6293189</v>
-      </c>
-      <c r="M2" t="n">
-        <v>5950086</v>
-      </c>
-      <c r="N2" t="n">
-        <v>93246143.36792</v>
-      </c>
-      <c r="O2" t="n">
-        <v>95423397</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1924268668</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>19999999</v>
-      </c>
-      <c r="R2" t="n">
-        <v>19999999</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="U2" t="n">
-        <v>95423397</v>
-      </c>
-      <c r="V2" t="n">
-        <v>95423397</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>95423397</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>95423397</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>95423397</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>9430580</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>104853977</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>5275078</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-48015</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>48015</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-6293189</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>343103</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>5950086</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>103479659</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>81373701</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>24809175</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>2046347</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2046347</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>16791506</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>6857916</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9933590</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>184853360</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1842894967</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2027748327</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2027748327</v>
-      </c>
+        <v>2941141</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-92050.044194</v>
+        <v>-70662.23664</v>
       </c>
       <c r="C3" t="n">
-        <v>0.101165</v>
+        <v>0.098125</v>
       </c>
       <c r="D3" t="n">
-        <v>123507018</v>
+        <v>101337638</v>
       </c>
       <c r="E3" t="n">
-        <v>-909896</v>
+        <v>-720127</v>
       </c>
       <c r="F3" t="n">
-        <v>-909896</v>
+        <v>-720127</v>
       </c>
       <c r="G3" t="n">
-        <v>88766985</v>
+        <v>75987371</v>
       </c>
       <c r="H3" t="n">
-        <v>19613281</v>
+        <v>15327156</v>
       </c>
       <c r="I3" t="n">
-        <v>1298774751</v>
+        <v>815042889</v>
       </c>
       <c r="J3" t="n">
-        <v>122597122</v>
+        <v>100617511</v>
       </c>
       <c r="K3" t="n">
-        <v>102983841</v>
+        <v>85290355</v>
       </c>
       <c r="L3" t="n">
-        <v>-4434406</v>
+        <v>-1201154</v>
       </c>
       <c r="M3" t="n">
-        <v>4225971</v>
+        <v>1035503</v>
       </c>
       <c r="N3" t="n">
-        <v>89584830.955806</v>
+        <v>76636835.76335999</v>
       </c>
       <c r="O3" t="n">
-        <v>88766985</v>
+        <v>75987371</v>
       </c>
       <c r="P3" t="n">
-        <v>1344997947</v>
+        <v>860161457</v>
       </c>
       <c r="Q3" t="n">
         <v>19999999</v>
@@ -854,141 +764,141 @@
         <v>19999999</v>
       </c>
       <c r="S3" t="n">
-        <v>4.44</v>
+        <v>3.799369</v>
       </c>
       <c r="T3" t="n">
-        <v>4.44</v>
+        <v>3.799369</v>
       </c>
       <c r="U3" t="n">
-        <v>88766985</v>
+        <v>75987371</v>
       </c>
       <c r="V3" t="n">
-        <v>88766985</v>
+        <v>75987371</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>88766985</v>
+        <v>75987371</v>
       </c>
       <c r="Y3" t="n">
-        <v>88766985</v>
+        <v>75987371</v>
       </c>
       <c r="Z3" t="n">
-        <v>88766985</v>
+        <v>75987371</v>
       </c>
       <c r="AA3" t="n">
-        <v>9990885</v>
+        <v>8267481</v>
       </c>
       <c r="AB3" t="n">
-        <v>98757870</v>
+        <v>84254852</v>
       </c>
       <c r="AC3" t="n">
-        <v>3090302</v>
+        <v>1608214</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2409779</v>
+        <v>-867240</v>
       </c>
       <c r="AE3" t="n">
-        <v>-106623</v>
+        <v>-54976</v>
       </c>
       <c r="AF3" t="n">
-        <v>2516402</v>
+        <v>922216</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4434406</v>
+        <v>-1201154</v>
       </c>
       <c r="AH3" t="n">
-        <v>208435</v>
+        <v>165651</v>
       </c>
       <c r="AI3" t="n">
-        <v>4225971</v>
+        <v>1035503</v>
       </c>
       <c r="AJ3" t="n">
-        <v>101011870</v>
+        <v>84567919</v>
       </c>
       <c r="AK3" t="n">
-        <v>46223196</v>
+        <v>45118568</v>
       </c>
       <c r="AL3" t="n">
-        <v>1197546</v>
+        <v>2772575</v>
       </c>
       <c r="AM3" t="n">
-        <v>1467787</v>
+        <v>1259416</v>
       </c>
       <c r="AN3" t="n">
-        <v>1467787</v>
+        <v>1259416</v>
       </c>
       <c r="AO3" t="n">
-        <v>11941095</v>
+        <v>10205771</v>
       </c>
       <c r="AP3" t="n">
-        <v>3379062</v>
+        <v>3568046</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8562033</v>
+        <v>6637725</v>
       </c>
       <c r="AR3" t="n">
-        <v>147235066</v>
+        <v>129686487</v>
       </c>
       <c r="AS3" t="n">
-        <v>1298774751</v>
+        <v>815042889</v>
       </c>
       <c r="AT3" t="n">
-        <v>1446009817</v>
+        <v>944729376</v>
       </c>
       <c r="AU3" t="n">
-        <v>1446009817</v>
+        <v>944729376</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-70662.23664</v>
+        <v>-92050.044194</v>
       </c>
       <c r="C4" t="n">
-        <v>0.098125</v>
+        <v>0.101165</v>
       </c>
       <c r="D4" t="n">
-        <v>101337638</v>
+        <v>123507018</v>
       </c>
       <c r="E4" t="n">
-        <v>-720127</v>
+        <v>-909896</v>
       </c>
       <c r="F4" t="n">
-        <v>-720127</v>
+        <v>-909896</v>
       </c>
       <c r="G4" t="n">
-        <v>75987371</v>
+        <v>88766985</v>
       </c>
       <c r="H4" t="n">
-        <v>15327156</v>
+        <v>19613281</v>
       </c>
       <c r="I4" t="n">
-        <v>815042889</v>
+        <v>1298774751</v>
       </c>
       <c r="J4" t="n">
-        <v>100617511</v>
+        <v>122597122</v>
       </c>
       <c r="K4" t="n">
-        <v>85290355</v>
+        <v>102983841</v>
       </c>
       <c r="L4" t="n">
-        <v>-1201154</v>
+        <v>-4434406</v>
       </c>
       <c r="M4" t="n">
-        <v>1035503</v>
+        <v>4225971</v>
       </c>
       <c r="N4" t="n">
-        <v>76636835.76335999</v>
+        <v>89584830.955806</v>
       </c>
       <c r="O4" t="n">
-        <v>75987371</v>
+        <v>88766985</v>
       </c>
       <c r="P4" t="n">
-        <v>860161457</v>
+        <v>1344997947</v>
       </c>
       <c r="Q4" t="n">
         <v>19999999</v>
@@ -997,139 +907,141 @@
         <v>19999999</v>
       </c>
       <c r="S4" t="n">
-        <v>3.799369</v>
+        <v>4.44</v>
       </c>
       <c r="T4" t="n">
-        <v>3.799369</v>
+        <v>4.44</v>
       </c>
       <c r="U4" t="n">
-        <v>75987371</v>
+        <v>88766985</v>
       </c>
       <c r="V4" t="n">
-        <v>75987371</v>
+        <v>88766985</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>75987371</v>
+        <v>88766985</v>
       </c>
       <c r="Y4" t="n">
-        <v>75987371</v>
+        <v>88766985</v>
       </c>
       <c r="Z4" t="n">
-        <v>75987371</v>
+        <v>88766985</v>
       </c>
       <c r="AA4" t="n">
-        <v>8267481</v>
+        <v>9990885</v>
       </c>
       <c r="AB4" t="n">
-        <v>84254852</v>
+        <v>98757870</v>
       </c>
       <c r="AC4" t="n">
-        <v>1608214</v>
+        <v>3090302</v>
       </c>
       <c r="AD4" t="n">
-        <v>-867240</v>
+        <v>-2409779</v>
       </c>
       <c r="AE4" t="n">
-        <v>-54976</v>
+        <v>-106623</v>
       </c>
       <c r="AF4" t="n">
-        <v>922216</v>
+        <v>2516402</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1201154</v>
+        <v>-4434406</v>
       </c>
       <c r="AH4" t="n">
-        <v>165651</v>
+        <v>208435</v>
       </c>
       <c r="AI4" t="n">
-        <v>1035503</v>
+        <v>4225971</v>
       </c>
       <c r="AJ4" t="n">
-        <v>84567919</v>
+        <v>101011870</v>
       </c>
       <c r="AK4" t="n">
-        <v>45118568</v>
+        <v>46223196</v>
       </c>
       <c r="AL4" t="n">
-        <v>2772575</v>
+        <v>1197546</v>
       </c>
       <c r="AM4" t="n">
-        <v>1259416</v>
+        <v>1467787</v>
       </c>
       <c r="AN4" t="n">
-        <v>1259416</v>
+        <v>1467787</v>
       </c>
       <c r="AO4" t="n">
-        <v>10205771</v>
+        <v>11941095</v>
       </c>
       <c r="AP4" t="n">
-        <v>3568046</v>
+        <v>3379062</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6637725</v>
+        <v>8562033</v>
       </c>
       <c r="AR4" t="n">
-        <v>129686487</v>
+        <v>147235066</v>
       </c>
       <c r="AS4" t="n">
-        <v>815042889</v>
+        <v>1298774751</v>
       </c>
       <c r="AT4" t="n">
-        <v>944729376</v>
+        <v>1446009817</v>
       </c>
       <c r="AU4" t="n">
-        <v>944729376</v>
+        <v>1446009817</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>41965.062098</v>
+        <v>221835.074558</v>
       </c>
       <c r="C5" t="n">
-        <v>0.108711</v>
+        <v>0.08994000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>72223287</v>
+        <v>130829471</v>
       </c>
       <c r="E5" t="n">
-        <v>386025</v>
+        <v>2466475</v>
       </c>
       <c r="F5" t="n">
-        <v>386025</v>
+        <v>2466475</v>
       </c>
       <c r="G5" t="n">
-        <v>55660953</v>
+        <v>95423397</v>
       </c>
       <c r="H5" t="n">
-        <v>13349542</v>
+        <v>22491883</v>
       </c>
       <c r="I5" t="n">
-        <v>566863723</v>
+        <v>1842894967</v>
       </c>
       <c r="J5" t="n">
-        <v>72609312</v>
+        <v>133295946</v>
       </c>
       <c r="K5" t="n">
-        <v>59259770</v>
+        <v>110804063</v>
       </c>
       <c r="L5" t="n">
-        <v>-137005</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>-6293189</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5950086</v>
+      </c>
       <c r="N5" t="n">
-        <v>55316893.062098</v>
+        <v>93178757.074558</v>
       </c>
       <c r="O5" t="n">
-        <v>55660953</v>
+        <v>95423397</v>
       </c>
       <c r="P5" t="n">
-        <v>604463379</v>
+        <v>1919541689</v>
       </c>
       <c r="Q5" t="n">
         <v>19999999</v>
@@ -1138,89 +1050,232 @@
         <v>19999999</v>
       </c>
       <c r="S5" t="n">
-        <v>2.783048</v>
+        <v>4.77</v>
       </c>
       <c r="T5" t="n">
-        <v>2.783048</v>
+        <v>4.77</v>
       </c>
       <c r="U5" t="n">
-        <v>55660953</v>
+        <v>95423397</v>
       </c>
       <c r="V5" t="n">
-        <v>55660953</v>
+        <v>95423397</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55660953</v>
+        <v>95423397</v>
       </c>
       <c r="Y5" t="n">
-        <v>55660953</v>
+        <v>95423397</v>
       </c>
       <c r="Z5" t="n">
-        <v>55660953</v>
+        <v>95423397</v>
       </c>
       <c r="AA5" t="n">
-        <v>6788978</v>
+        <v>9430580</v>
       </c>
       <c r="AB5" t="n">
-        <v>62449931</v>
+        <v>104853977</v>
       </c>
       <c r="AC5" t="n">
-        <v>2941141</v>
+        <v>474053</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1884</v>
+        <v>26031</v>
       </c>
       <c r="AE5" t="n">
-        <v>1884</v>
+        <v>-26031</v>
       </c>
       <c r="AF5" t="n">
-        <v>8716746</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>-137005</v>
+        <v>-6293189</v>
       </c>
       <c r="AH5" t="n">
-        <v>137005</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>343103</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5950086</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>59259770</v>
+        <v>108206638</v>
       </c>
       <c r="AK5" t="n">
-        <v>37599656</v>
+        <v>76646722</v>
       </c>
       <c r="AL5" t="n">
-        <v>7747077</v>
+        <v>24809175</v>
       </c>
       <c r="AM5" t="n">
-        <v>1376493</v>
+        <v>2046347</v>
       </c>
       <c r="AN5" t="n">
-        <v>1376493</v>
+        <v>2046347</v>
       </c>
       <c r="AO5" t="n">
-        <v>6617882</v>
+        <v>16791506</v>
       </c>
       <c r="AP5" t="n">
-        <v>1510817</v>
+        <v>6857916</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5107065</v>
+        <v>9933590</v>
       </c>
       <c r="AR5" t="n">
-        <v>96859426</v>
+        <v>184853360</v>
       </c>
       <c r="AS5" t="n">
-        <v>566863723</v>
+        <v>1842894967</v>
       </c>
       <c r="AT5" t="n">
-        <v>663723149</v>
+        <v>2027748327</v>
       </c>
       <c r="AU5" t="n">
-        <v>663723149</v>
+        <v>2027748327</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-159781.128616</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.07178900000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>189959385</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2225714</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2225714</v>
+      </c>
+      <c r="G6" t="n">
+        <v>138464882</v>
+      </c>
+      <c r="H6" t="n">
+        <v>29792845</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2375123923</v>
+      </c>
+      <c r="J6" t="n">
+        <v>187733671</v>
+      </c>
+      <c r="K6" t="n">
+        <v>157940826</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-9118576</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8766944</v>
+      </c>
+      <c r="N6" t="n">
+        <v>140530814.871384</v>
+      </c>
+      <c r="O6" t="n">
+        <v>138464882</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2451602295</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>26666666</v>
+      </c>
+      <c r="R6" t="n">
+        <v>26666666</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="U6" t="n">
+        <v>138464882</v>
+      </c>
+      <c r="V6" t="n">
+        <v>138464882</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>138464882</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>138464882</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>138464882</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>10709000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>149173882</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>-5160681</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-139388</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>5300069</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-9118576</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>351632</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>8766944</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>159391505</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>76478372</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>9678403</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1879701</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1879701</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>25882867</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>11235149</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>14647718</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>235869877</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2375123923</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2610993800</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2610993800</v>
       </c>
     </row>
   </sheetData>
@@ -1234,7 +1289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1533,186 +1588,96 @@
           <t>Cash Financial</t>
         </is>
       </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>Cash Equivalents</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>19999999</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19999999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>54926684</v>
-      </c>
-      <c r="F2" t="n">
-        <v>396693744</v>
-      </c>
-      <c r="G2" t="n">
-        <v>398012191</v>
-      </c>
-      <c r="H2" t="n">
-        <v>348801393</v>
-      </c>
-      <c r="I2" t="n">
-        <v>396693744</v>
-      </c>
-      <c r="J2" t="n">
-        <v>54926684</v>
-      </c>
-      <c r="K2" t="n">
-        <v>398012191</v>
-      </c>
-      <c r="L2" t="n">
-        <v>398012191</v>
-      </c>
-      <c r="M2" t="n">
-        <v>398012191</v>
-      </c>
-      <c r="N2" t="n">
-        <v>398012191</v>
-      </c>
-      <c r="O2" t="n">
-        <v>203012191</v>
-      </c>
-      <c r="P2" t="n">
-        <v>150000000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>150000000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>462337239</v>
-      </c>
-      <c r="S2" t="n">
-        <v>125439762</v>
-      </c>
-      <c r="T2" t="n">
-        <v>923061</v>
-      </c>
-      <c r="U2" t="n">
-        <v>89218333</v>
-      </c>
-      <c r="V2" t="n">
-        <v>35298368</v>
-      </c>
-      <c r="W2" t="n">
-        <v>35298368</v>
-      </c>
-      <c r="X2" t="n">
-        <v>336897477</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>18492576</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>10752278</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>19628316</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>19628316</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>129325670</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>23784572</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>5103636</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>8676018</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10004918</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>860349430</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>174650560</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>50585057</v>
-      </c>
+        <v>3649705</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>1318447</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1318447</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>72858828</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-60042122</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>132900950</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>66879289</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>60677506</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5344155</v>
-      </c>
-      <c r="AV2" t="n">
+      <c r="AL2" t="n">
         <v>0</v>
       </c>
-      <c r="AW2" t="n">
-        <v>685698870</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>122940904</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>25873600</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>71612105</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>278452809</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-47680745</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>326133554</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>186819452</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>82509636</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>104309816</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>104309816</v>
-      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="n">
+        <v>45623027</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+        <v>44926</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>19999999</v>
       </c>
@@ -1720,37 +1685,37 @@
         <v>19999999</v>
       </c>
       <c r="E3" t="n">
-        <v>40728024</v>
+        <v>20828828</v>
       </c>
       <c r="F3" t="n">
-        <v>342478154</v>
+        <v>291691665</v>
       </c>
       <c r="G3" t="n">
-        <v>343884860</v>
+        <v>293065702</v>
       </c>
       <c r="H3" t="n">
-        <v>293281670</v>
+        <v>246128794</v>
       </c>
       <c r="I3" t="n">
-        <v>342478154</v>
+        <v>291691665</v>
       </c>
       <c r="J3" t="n">
-        <v>40728024</v>
+        <v>20828828</v>
       </c>
       <c r="K3" t="n">
-        <v>343884860</v>
+        <v>293065702</v>
       </c>
       <c r="L3" t="n">
-        <v>343884860</v>
+        <v>293065702</v>
       </c>
       <c r="M3" t="n">
-        <v>343884860</v>
+        <v>293065702</v>
       </c>
       <c r="N3" t="n">
-        <v>343884860</v>
+        <v>293065702</v>
       </c>
       <c r="O3" t="n">
-        <v>149714749</v>
+        <v>107772290</v>
       </c>
       <c r="P3" t="n">
         <v>150000000</v>
@@ -1759,87 +1724,91 @@
         <v>150000000</v>
       </c>
       <c r="R3" t="n">
-        <v>332729820</v>
+        <v>211032886</v>
       </c>
       <c r="S3" t="n">
-        <v>93753210</v>
+        <v>36938679</v>
       </c>
       <c r="T3" t="n">
-        <v>1023481</v>
+        <v>1178329</v>
       </c>
       <c r="U3" t="n">
-        <v>66338872</v>
+        <v>25602457</v>
       </c>
       <c r="V3" t="n">
-        <v>26390857</v>
+        <v>10157893</v>
       </c>
       <c r="W3" t="n">
-        <v>26390857</v>
+        <v>10157893</v>
       </c>
       <c r="X3" t="n">
-        <v>238976610</v>
+        <v>174094207</v>
       </c>
       <c r="Y3" t="n">
-        <v>11772204</v>
+        <v>12208106</v>
       </c>
       <c r="Z3" t="n">
-        <v>10250340</v>
+        <v>8463346</v>
       </c>
       <c r="AA3" t="n">
-        <v>14337167</v>
+        <v>10670935</v>
       </c>
       <c r="AB3" t="n">
-        <v>14337167</v>
+        <v>10670935</v>
       </c>
       <c r="AC3" t="n">
-        <v>88046656</v>
+        <v>45166614</v>
       </c>
       <c r="AD3" t="n">
-        <v>22059333</v>
+        <v>27279873</v>
       </c>
       <c r="AE3" t="n">
-        <v>4802702</v>
+        <v>3385719</v>
       </c>
       <c r="AF3" t="n">
-        <v>7886729</v>
+        <v>12918889</v>
       </c>
       <c r="AG3" t="n">
-        <v>9369902</v>
+        <v>10975265</v>
       </c>
       <c r="AH3" t="n">
-        <v>676614680</v>
+        <v>504098588</v>
       </c>
       <c r="AI3" t="n">
-        <v>144356400</v>
+        <v>83875587</v>
       </c>
       <c r="AJ3" t="n">
-        <v>44815225</v>
+        <v>46603184</v>
       </c>
       <c r="AK3" t="n">
-        <v>39645935</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>4027500</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>4027500</v>
+      </c>
       <c r="AN3" t="n">
-        <v>1406706</v>
+        <v>1374037</v>
       </c>
       <c r="AO3" t="n">
-        <v>1406706</v>
+        <v>1374037</v>
       </c>
       <c r="AP3" t="n">
-        <v>58488534</v>
+        <v>35898366</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-62748999</v>
+        <v>-47591802</v>
       </c>
       <c r="AR3" t="n">
-        <v>121237533</v>
+        <v>83490168</v>
       </c>
       <c r="AS3" t="n">
-        <v>56488918</v>
+        <v>43737660</v>
       </c>
       <c r="AT3" t="n">
-        <v>59404460</v>
+        <v>34408353</v>
       </c>
       <c r="AU3" t="n">
         <v>5344155</v>
@@ -1848,47 +1817,51 @@
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>532258280</v>
+        <v>420223001</v>
       </c>
       <c r="AX3" t="n">
-        <v>114304075</v>
+        <v>93425043</v>
       </c>
       <c r="AY3" t="n">
-        <v>18935599</v>
+        <v>15970063</v>
       </c>
       <c r="AZ3" t="n">
-        <v>37627152</v>
+        <v>79654109</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>41118707</v>
       </c>
       <c r="BB3" t="n">
-        <v>214644186</v>
+        <v>210300730</v>
       </c>
       <c r="BC3" t="n">
-        <v>-29047631</v>
+        <v>-28810042</v>
       </c>
       <c r="BD3" t="n">
-        <v>243691817</v>
+        <v>239110772</v>
       </c>
       <c r="BE3" t="n">
-        <v>146747268</v>
+        <v>59408458</v>
       </c>
       <c r="BF3" t="n">
-        <v>65289751</v>
+        <v>4027500</v>
       </c>
       <c r="BG3" t="n">
-        <v>81457517</v>
+        <v>55380958</v>
       </c>
       <c r="BH3" t="n">
-        <v>81457517</v>
-      </c>
+        <v>55380958</v>
+      </c>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
         <v>19999999</v>
       </c>
@@ -1896,37 +1869,37 @@
         <v>19999999</v>
       </c>
       <c r="E4" t="n">
-        <v>20828828</v>
+        <v>40728024</v>
       </c>
       <c r="F4" t="n">
-        <v>291691665</v>
+        <v>342478154</v>
       </c>
       <c r="G4" t="n">
-        <v>293065702</v>
+        <v>343884860</v>
       </c>
       <c r="H4" t="n">
-        <v>246128794</v>
+        <v>293281670</v>
       </c>
       <c r="I4" t="n">
-        <v>291691665</v>
+        <v>342478154</v>
       </c>
       <c r="J4" t="n">
-        <v>20828828</v>
+        <v>40728024</v>
       </c>
       <c r="K4" t="n">
-        <v>293065702</v>
+        <v>343884860</v>
       </c>
       <c r="L4" t="n">
-        <v>293065702</v>
+        <v>343884860</v>
       </c>
       <c r="M4" t="n">
-        <v>293065702</v>
+        <v>343884860</v>
       </c>
       <c r="N4" t="n">
-        <v>293065702</v>
+        <v>343884860</v>
       </c>
       <c r="O4" t="n">
-        <v>107772290</v>
+        <v>149714749</v>
       </c>
       <c r="P4" t="n">
         <v>150000000</v>
@@ -1935,91 +1908,87 @@
         <v>150000000</v>
       </c>
       <c r="R4" t="n">
-        <v>211032886</v>
+        <v>332729820</v>
       </c>
       <c r="S4" t="n">
-        <v>36938679</v>
+        <v>93753210</v>
       </c>
       <c r="T4" t="n">
-        <v>1178329</v>
+        <v>1023481</v>
       </c>
       <c r="U4" t="n">
-        <v>25602457</v>
+        <v>66338872</v>
       </c>
       <c r="V4" t="n">
-        <v>10157893</v>
+        <v>26390857</v>
       </c>
       <c r="W4" t="n">
-        <v>10157893</v>
+        <v>26390857</v>
       </c>
       <c r="X4" t="n">
-        <v>174094207</v>
+        <v>238976610</v>
       </c>
       <c r="Y4" t="n">
-        <v>12208106</v>
+        <v>11772204</v>
       </c>
       <c r="Z4" t="n">
-        <v>8463346</v>
+        <v>10250340</v>
       </c>
       <c r="AA4" t="n">
-        <v>10670935</v>
+        <v>14337167</v>
       </c>
       <c r="AB4" t="n">
-        <v>10670935</v>
+        <v>14337167</v>
       </c>
       <c r="AC4" t="n">
-        <v>45166614</v>
+        <v>88046656</v>
       </c>
       <c r="AD4" t="n">
-        <v>27279873</v>
+        <v>22059333</v>
       </c>
       <c r="AE4" t="n">
-        <v>3385719</v>
+        <v>4802702</v>
       </c>
       <c r="AF4" t="n">
-        <v>12918889</v>
+        <v>7886729</v>
       </c>
       <c r="AG4" t="n">
-        <v>10975265</v>
+        <v>9369902</v>
       </c>
       <c r="AH4" t="n">
-        <v>504098588</v>
+        <v>676614680</v>
       </c>
       <c r="AI4" t="n">
-        <v>83875587</v>
+        <v>144356400</v>
       </c>
       <c r="AJ4" t="n">
-        <v>46603184</v>
+        <v>44815225</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>4027500</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>4027500</v>
-      </c>
+        <v>39645935</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>1374037</v>
+        <v>1406706</v>
       </c>
       <c r="AO4" t="n">
-        <v>1374037</v>
+        <v>1406706</v>
       </c>
       <c r="AP4" t="n">
-        <v>35898366</v>
+        <v>58488534</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-47591802</v>
+        <v>-62748999</v>
       </c>
       <c r="AR4" t="n">
-        <v>83490168</v>
+        <v>121237533</v>
       </c>
       <c r="AS4" t="n">
-        <v>43737660</v>
+        <v>56488918</v>
       </c>
       <c r="AT4" t="n">
-        <v>34408353</v>
+        <v>59404460</v>
       </c>
       <c r="AU4" t="n">
         <v>5344155</v>
@@ -2028,45 +1997,47 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>420223001</v>
+        <v>532258280</v>
       </c>
       <c r="AX4" t="n">
-        <v>93425043</v>
+        <v>114304075</v>
       </c>
       <c r="AY4" t="n">
-        <v>15970063</v>
+        <v>18935599</v>
       </c>
       <c r="AZ4" t="n">
-        <v>79654109</v>
+        <v>37627152</v>
       </c>
       <c r="BA4" t="n">
-        <v>41118707</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>210300730</v>
+        <v>214644186</v>
       </c>
       <c r="BC4" t="n">
-        <v>-28810042</v>
+        <v>-29047631</v>
       </c>
       <c r="BD4" t="n">
-        <v>239110772</v>
+        <v>243691817</v>
       </c>
       <c r="BE4" t="n">
-        <v>59408458</v>
+        <v>146747268</v>
       </c>
       <c r="BF4" t="n">
-        <v>4027500</v>
+        <v>65289751</v>
       </c>
       <c r="BG4" t="n">
-        <v>55380958</v>
+        <v>81457517</v>
       </c>
       <c r="BH4" t="n">
-        <v>55380958</v>
-      </c>
+        <v>81457517</v>
+      </c>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
@@ -2076,128 +2047,124 @@
         <v>19999999</v>
       </c>
       <c r="E5" t="n">
-        <v>19511114</v>
+        <v>54926684</v>
       </c>
       <c r="F5" t="n">
-        <v>231237466</v>
+        <v>396693744</v>
       </c>
       <c r="G5" t="n">
-        <v>233024122</v>
+        <v>398012191</v>
       </c>
       <c r="H5" t="n">
-        <v>193766364</v>
+        <v>348801393</v>
       </c>
       <c r="I5" t="n">
-        <v>231237466</v>
+        <v>396693744</v>
       </c>
       <c r="J5" t="n">
-        <v>19511114</v>
+        <v>54926684</v>
       </c>
       <c r="K5" t="n">
-        <v>233024122</v>
+        <v>398012191</v>
       </c>
       <c r="L5" t="n">
-        <v>233024122</v>
+        <v>398012191</v>
       </c>
       <c r="M5" t="n">
-        <v>233024122</v>
+        <v>398012191</v>
       </c>
       <c r="N5" t="n">
-        <v>233024122</v>
+        <v>398012191</v>
       </c>
       <c r="O5" t="n">
-        <v>85329447</v>
+        <v>203012191</v>
       </c>
       <c r="P5" t="n">
-        <v>100000000</v>
+        <v>150000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>100000000</v>
+        <v>150000000</v>
       </c>
       <c r="R5" t="n">
-        <v>172021167</v>
+        <v>462337239</v>
       </c>
       <c r="S5" t="n">
-        <v>36052865</v>
+        <v>125439762</v>
       </c>
       <c r="T5" t="n">
-        <v>1172976</v>
+        <v>923061</v>
       </c>
       <c r="U5" t="n">
-        <v>27584798</v>
+        <v>89218333</v>
       </c>
       <c r="V5" t="n">
-        <v>7295091</v>
+        <v>35298368</v>
       </c>
       <c r="W5" t="n">
-        <v>7295091</v>
+        <v>35298368</v>
       </c>
       <c r="X5" t="n">
-        <v>135968302</v>
+        <v>336897477</v>
       </c>
       <c r="Y5" t="n">
-        <v>12205803</v>
+        <v>18492576</v>
       </c>
       <c r="Z5" t="n">
-        <v>6787961</v>
+        <v>10752278</v>
       </c>
       <c r="AA5" t="n">
-        <v>12216023</v>
+        <v>19628316</v>
       </c>
       <c r="AB5" t="n">
-        <v>12216023</v>
+        <v>19628316</v>
       </c>
       <c r="AC5" t="n">
-        <v>39922355</v>
+        <v>129325670</v>
       </c>
       <c r="AD5" t="n">
-        <v>22606763</v>
+        <v>18680936</v>
       </c>
       <c r="AE5" t="n">
-        <v>3649705</v>
+        <v>5103636</v>
       </c>
       <c r="AF5" t="n">
-        <v>8377238</v>
+        <v>8676018</v>
       </c>
       <c r="AG5" t="n">
-        <v>10579820</v>
+        <v>10004918</v>
       </c>
       <c r="AH5" t="n">
-        <v>405045289</v>
+        <v>860349430</v>
       </c>
       <c r="AI5" t="n">
-        <v>75310623</v>
+        <v>174650560</v>
       </c>
       <c r="AJ5" t="n">
-        <v>41444235</v>
+        <v>50585057</v>
       </c>
       <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>1786656</v>
+        <v>1318447</v>
       </c>
       <c r="AO5" t="n">
-        <v>1786656</v>
+        <v>1318447</v>
       </c>
       <c r="AP5" t="n">
-        <v>32079732</v>
+        <v>72858828</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-37158570</v>
+        <v>-60042122</v>
       </c>
       <c r="AR5" t="n">
-        <v>69238302</v>
+        <v>132900950</v>
       </c>
       <c r="AS5" t="n">
-        <v>37128983</v>
+        <v>66879289</v>
       </c>
       <c r="AT5" t="n">
-        <v>26765164</v>
+        <v>60677506</v>
       </c>
       <c r="AU5" t="n">
         <v>5344155</v>
@@ -2206,40 +2173,218 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>329734666</v>
+        <v>685698870</v>
       </c>
       <c r="AX5" t="n">
-        <v>80260164</v>
+        <v>122940904</v>
       </c>
       <c r="AY5" t="n">
-        <v>10281785</v>
+        <v>25873600</v>
       </c>
       <c r="AZ5" t="n">
-        <v>52390288</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>45623027</v>
-      </c>
+        <v>71612105</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>84164341</v>
+        <v>278452809</v>
       </c>
       <c r="BC5" t="n">
-        <v>-28519911</v>
+        <v>-47680745</v>
       </c>
       <c r="BD5" t="n">
-        <v>112684252</v>
+        <v>326133554</v>
       </c>
       <c r="BE5" t="n">
-        <v>57015061</v>
+        <v>186819452</v>
       </c>
       <c r="BF5" t="n">
-        <v>30387909</v>
+        <v>82509636</v>
       </c>
       <c r="BG5" t="n">
-        <v>26627152</v>
+        <v>104309816</v>
       </c>
       <c r="BH5" t="n">
-        <v>26627152</v>
+        <v>104309816</v>
+      </c>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>19999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>19999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>60935963</v>
+      </c>
+      <c r="F6" t="n">
+        <v>505347869</v>
+      </c>
+      <c r="G6" t="n">
+        <v>506036462</v>
+      </c>
+      <c r="H6" t="n">
+        <v>437572971</v>
+      </c>
+      <c r="I6" t="n">
+        <v>505347869</v>
+      </c>
+      <c r="J6" t="n">
+        <v>60935963</v>
+      </c>
+      <c r="K6" t="n">
+        <v>506036462</v>
+      </c>
+      <c r="L6" t="n">
+        <v>506036462</v>
+      </c>
+      <c r="M6" t="n">
+        <v>506036462</v>
+      </c>
+      <c r="N6" t="n">
+        <v>506036462</v>
+      </c>
+      <c r="O6" t="n">
+        <v>356036462</v>
+      </c>
+      <c r="P6" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>608803146</v>
+      </c>
+      <c r="S6" t="n">
+        <v>169472733</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1386038</v>
+      </c>
+      <c r="U6" t="n">
+        <v>132768491</v>
+      </c>
+      <c r="V6" t="n">
+        <v>35318204</v>
+      </c>
+      <c r="W6" t="n">
+        <v>35318204</v>
+      </c>
+      <c r="X6" t="n">
+        <v>439330413</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>20229477</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>12348029</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>25617759</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>25617759</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>167319133</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>26890975</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>10675502</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>16215473</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1114839608</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>237936224</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>50124699</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>20436000</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>688593</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>688593</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>76946837</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-60495971</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>137442808</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>76324999</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>55773654</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5344155</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>876903384</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>164319871</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>38213990</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>98710503</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>372363845</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-54114044</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>426477889</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>203295175</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>46140271</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>157154904</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>47154904</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>20436000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>110000000</v>
       </c>
     </row>
   </sheetData>
@@ -2253,7 +2398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2422,407 +2567,467 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Dividends Received Cfi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>75733087</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-3418439</v>
-      </c>
-      <c r="D2" t="n">
-        <v>104309816</v>
-      </c>
-      <c r="E2" t="n">
-        <v>81457517</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22852299</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-52901733</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-33750000</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>-3397494</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>-600400</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-600400</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-2797094</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>20945</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-2818039</v>
-      </c>
-      <c r="S2" t="n">
-        <v>79151526</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-8928642</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-3469734</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-61825346</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-4840199</v>
-      </c>
-      <c r="X2" t="n">
-        <v>91097727</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-15574830</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-132508044</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>5876040</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>22491883</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>688659</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>21803224</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>36943475</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-2219885</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>48015</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>104853977</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>-20000000</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>15097903</v>
+      </c>
+      <c r="L2" t="n">
+        <v>45097903</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-30000000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>80931163</v>
+        <v>62662878</v>
       </c>
       <c r="C3" t="n">
-        <v>-4873960</v>
+        <v>-3446873</v>
       </c>
       <c r="D3" t="n">
-        <v>81457517</v>
+        <v>55380958</v>
       </c>
       <c r="E3" t="n">
-        <v>55380958</v>
+        <v>26627152</v>
       </c>
       <c r="F3" t="n">
-        <v>26076559</v>
+        <v>28753806</v>
       </c>
       <c r="G3" t="n">
-        <v>-55043773</v>
+        <v>-34020627</v>
       </c>
       <c r="H3" t="n">
-        <v>-37500000</v>
+        <v>-20000000</v>
       </c>
       <c r="I3" t="n">
-        <v>-37500000</v>
+        <v>-20000000</v>
       </c>
       <c r="J3" t="n">
-        <v>-4684791</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+        <v>-3335318</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26507522</v>
+      </c>
+      <c r="L3" t="n">
+        <v>43507522</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-17000000</v>
+      </c>
       <c r="N3" t="n">
-        <v>-672485</v>
+        <v>-242350</v>
       </c>
       <c r="O3" t="n">
-        <v>-672485</v>
+        <v>-242350</v>
       </c>
       <c r="P3" t="n">
-        <v>-4012306</v>
+        <v>-3092968</v>
       </c>
       <c r="Q3" t="n">
-        <v>189169</v>
+        <v>111555</v>
       </c>
       <c r="R3" t="n">
-        <v>-4201475</v>
+        <v>-3204523</v>
       </c>
       <c r="S3" t="n">
-        <v>85805123</v>
+        <v>66109751</v>
       </c>
       <c r="T3" t="n">
-        <v>-8203891</v>
+        <v>-6592096</v>
       </c>
       <c r="U3" t="n">
-        <v>-2323358</v>
+        <v>-1035503</v>
       </c>
       <c r="V3" t="n">
-        <v>2608321</v>
+        <v>-58583395</v>
       </c>
       <c r="W3" t="n">
-        <v>1781868</v>
+        <v>-5891227</v>
       </c>
       <c r="X3" t="n">
-        <v>59280419</v>
+        <v>38733239</v>
       </c>
       <c r="Y3" t="n">
-        <v>14757738</v>
+        <v>-15271053</v>
       </c>
       <c r="Z3" t="n">
-        <v>-73211704</v>
+        <v>-76154354</v>
       </c>
       <c r="AA3" t="n">
-        <v>4224236</v>
+        <v>1030967</v>
       </c>
       <c r="AB3" t="n">
-        <v>19613281</v>
+        <v>15327156</v>
       </c>
       <c r="AC3" t="n">
-        <v>639815</v>
+        <v>654969</v>
       </c>
       <c r="AD3" t="n">
-        <v>18973466</v>
+        <v>14672187</v>
       </c>
       <c r="AE3" t="n">
-        <v>45390210</v>
+        <v>8074190</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1252039</v>
+        <v>-147113</v>
       </c>
       <c r="AG3" t="n">
-        <v>-106623</v>
+        <v>-54976</v>
       </c>
       <c r="AH3" t="n">
-        <v>98757870</v>
-      </c>
+        <v>84254852</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>62662878</v>
+        <v>80931163</v>
       </c>
       <c r="C4" t="n">
-        <v>-3446873</v>
+        <v>-4873960</v>
       </c>
       <c r="D4" t="n">
+        <v>81457517</v>
+      </c>
+      <c r="E4" t="n">
         <v>55380958</v>
       </c>
-      <c r="E4" t="n">
-        <v>26627152</v>
-      </c>
       <c r="F4" t="n">
-        <v>28753806</v>
+        <v>26076559</v>
       </c>
       <c r="G4" t="n">
-        <v>-34020627</v>
+        <v>-55043773</v>
       </c>
       <c r="H4" t="n">
-        <v>-20000000</v>
+        <v>-37500000</v>
       </c>
       <c r="I4" t="n">
-        <v>-20000000</v>
+        <v>-37500000</v>
       </c>
       <c r="J4" t="n">
-        <v>-3335318</v>
-      </c>
-      <c r="K4" t="n">
-        <v>26507522</v>
-      </c>
-      <c r="L4" t="n">
-        <v>43507522</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-17000000</v>
-      </c>
+        <v>-4684791</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>-242350</v>
+        <v>-672485</v>
       </c>
       <c r="O4" t="n">
-        <v>-242350</v>
+        <v>-672485</v>
       </c>
       <c r="P4" t="n">
-        <v>-3092968</v>
+        <v>-4012306</v>
       </c>
       <c r="Q4" t="n">
-        <v>111555</v>
+        <v>189169</v>
       </c>
       <c r="R4" t="n">
-        <v>-3204523</v>
+        <v>-4201475</v>
       </c>
       <c r="S4" t="n">
-        <v>66109751</v>
+        <v>85805123</v>
       </c>
       <c r="T4" t="n">
-        <v>-6592096</v>
+        <v>-8203891</v>
       </c>
       <c r="U4" t="n">
-        <v>-1035503</v>
+        <v>-2323358</v>
       </c>
       <c r="V4" t="n">
-        <v>-58583395</v>
+        <v>2608321</v>
       </c>
       <c r="W4" t="n">
-        <v>-5891227</v>
+        <v>1781868</v>
       </c>
       <c r="X4" t="n">
-        <v>38733239</v>
+        <v>59280419</v>
       </c>
       <c r="Y4" t="n">
-        <v>-15271053</v>
+        <v>14757738</v>
       </c>
       <c r="Z4" t="n">
-        <v>-76154354</v>
+        <v>-73211704</v>
       </c>
       <c r="AA4" t="n">
-        <v>1030967</v>
+        <v>4224236</v>
       </c>
       <c r="AB4" t="n">
-        <v>15327156</v>
+        <v>19613281</v>
       </c>
       <c r="AC4" t="n">
-        <v>654969</v>
+        <v>639815</v>
       </c>
       <c r="AD4" t="n">
-        <v>14672187</v>
+        <v>18973466</v>
       </c>
       <c r="AE4" t="n">
-        <v>8074190</v>
+        <v>45390210</v>
       </c>
       <c r="AF4" t="n">
-        <v>-147113</v>
+        <v>-1252039</v>
       </c>
       <c r="AG4" t="n">
-        <v>-54976</v>
+        <v>-106623</v>
       </c>
       <c r="AH4" t="n">
-        <v>84254852</v>
-      </c>
+        <v>98757870</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-21048627</v>
+        <v>75733087</v>
       </c>
       <c r="C5" t="n">
-        <v>-1978540</v>
+        <v>-3418439</v>
       </c>
       <c r="D5" t="n">
-        <v>26627152</v>
+        <v>104309816</v>
       </c>
       <c r="E5" t="n">
-        <v>63885734</v>
+        <v>81457517</v>
       </c>
       <c r="F5" t="n">
-        <v>-37258582</v>
+        <v>22852299</v>
       </c>
       <c r="G5" t="n">
-        <v>-31315488</v>
+        <v>-52901733</v>
       </c>
       <c r="H5" t="n">
+        <v>-33750000</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>-3397494</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-600400</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-600400</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-2797094</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>20945</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-2818039</v>
+      </c>
+      <c r="S5" t="n">
+        <v>79151526</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-8928642</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-3469734</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-61825346</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-4840199</v>
+      </c>
+      <c r="X5" t="n">
+        <v>91097727</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-15574830</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-132508044</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5876040</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>22491883</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>688659</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>21803224</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>36943475</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-2219885</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>48015</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>104853977</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>136183298</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1637456</v>
+      </c>
+      <c r="D6" t="n">
+        <v>157154904</v>
+      </c>
+      <c r="E6" t="n">
+        <v>104309816</v>
+      </c>
+      <c r="F6" t="n">
+        <v>52845088</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-64523529</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-39000000</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>-20452137</v>
+      </c>
+      <c r="K6" t="n">
         <v>-20000000</v>
       </c>
-      <c r="I5" t="n">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
         <v>-20000000</v>
       </c>
-      <c r="J5" t="n">
-        <v>13126993</v>
-      </c>
-      <c r="K5" t="n">
-        <v>15097903</v>
-      </c>
-      <c r="L5" t="n">
-        <v>45097903</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-30000000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-1187295</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-1187295</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-783615</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7630</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-791245</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-19070087</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-6625936</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-1069639</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-100454677</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-41205932</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4302148</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-51429806</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-12121087</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1069639</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>13349542</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>712948</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>12636594</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>10450269</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-387909</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>66197</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>62449931</v>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-1578804</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>58652</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1637456</v>
+      </c>
+      <c r="S6" t="n">
+        <v>137820754</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-9113249</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-4488918</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-133103098</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-265595</v>
+      </c>
+      <c r="X6" t="n">
+        <v>96036672</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-59019426</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-169854749</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>8669201</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>29792845</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>629854</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>29162991</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>59686396</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-3981982</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-41645</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>149173882</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1126667</v>
       </c>
     </row>
   </sheetData>
@@ -2836,7 +3041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EQ2"/>
+  <dimension ref="A1:EO2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2967,610 +3172,600 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>dividendRate</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>dividendYield</t>
+          <t>trailingPE</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>trailingPE</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>forwardPE</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>forwardPE</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>lastSplitFactor</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>earningsQuarterlyGrowth</t>
+          <t>lastSplitDate</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>lastSplitFactor</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>lastSplitDate</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>targetHighPrice</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>targetLowPrice</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>targetMeanPrice</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>targetMedianPrice</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>targetHighPrice</t>
+          <t>recommendationMean</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>targetLowPrice</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>targetMeanPrice</t>
+          <t>numberOfAnalystOpinions</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>targetMedianPrice</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>numberOfAnalystOpinions</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>earningsGrowth</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>earningsGrowth</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>marketState</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>corporateActions</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>regularMarketTime</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
       <c r="EE1" t="inlineStr">
         <is>
-          <t>esgPopulated</t>
+          <t>fiftyDayAverageChange</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
         <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
       <c r="EM1" t="inlineStr">
         <is>
-          <t>exchangeDataDelayedBy</t>
+          <t>regularMarketChangePercent</t>
         </is>
       </c>
       <c r="EN1" t="inlineStr">
         <is>
-          <t>marketState</t>
+          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EO1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3592,10 +3787,8 @@
           <t>Riyadh</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>11679</t>
-        </is>
+      <c r="D2" t="n">
+        <v>11679</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3644,7 +3837,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Engineer Riyad Ibrahim Al-Rumaizan', 'title': 'CEO &amp; Non-Independent Director', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Tarek Fouad Mahmoud', 'title': 'Chief Financial Officer', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Fahd  Alobisi', 'title': 'GM of Operations', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Khaled Hussain Fatani', 'age': 59, 'title': 'Acting Executive Director of Recruitment &amp; International Relations', 'yearBorn': 1966, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Anas Sameer Alhaj', 'age': 42, 'title': 'Executive Director of Individuals Sales &amp; Operation', 'yearBorn': 1983, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mohammed Sammer Haj', 'age': 41, 'title': 'Executive Director of Corporate Sales', 'yearBorn': 1984, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Engineer Riyad Ibrahim Al-Rumaizan', 'title': 'CEO &amp; Non-Independent Director', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Tarek Fouad Mahmoud', 'title': 'Chief Financial Officer', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Fahd  Alobisi', 'title': 'GM of Operations', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Abdulaziz Saleh-Mohammed Alsowail', 'age': 47, 'title': 'Executive Vice President', 'yearBorn': 1978, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Khaled Hussain Fatani', 'age': 59, 'title': 'Acting Executive Director of Recruitment &amp; International Relations', 'yearBorn': 1966, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Anas Sameer Alhaj', 'age': 42, 'title': 'Executive Director of Individuals Sales &amp; Operation', 'yearBorn': 1983, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mohammed Sammer Haj', 'age': 41, 'title': 'Executive Director of Corporate Sales', 'yearBorn': 1984, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -3659,439 +3852,435 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>95.90000000000001</v>
+        <v>102</v>
       </c>
       <c r="S2" t="n">
-        <v>95.59999999999999</v>
+        <v>101.8</v>
       </c>
       <c r="T2" t="n">
-        <v>94.34999999999999</v>
+        <v>101</v>
       </c>
       <c r="U2" t="n">
-        <v>96</v>
+        <v>103.4</v>
       </c>
       <c r="V2" t="n">
-        <v>95.90000000000001</v>
+        <v>102</v>
       </c>
       <c r="W2" t="n">
-        <v>95.59999999999999</v>
+        <v>101.8</v>
       </c>
       <c r="X2" t="n">
-        <v>94.34999999999999</v>
+        <v>101</v>
       </c>
       <c r="Y2" t="n">
-        <v>96</v>
+        <v>103.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.8</v>
+        <v>0.274</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.92</v>
+        <v>16.126984</v>
       </c>
       <c r="AB2" t="n">
+        <v>112060</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>112060</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>179872</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>192856</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>192856</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2032000000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2032000000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>73</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>111.525</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.7307242</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>91.655</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>92.87762499999999</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2.063</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.02022549</v>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="AU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1884391552</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>10.381913</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.057789996</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9195000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.52927</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.008580000000000001</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>26.641</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>3.8136704</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1774915200</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>160711232</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="BM2" t="n">
+        <v>1770768000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.018546343</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.2568333</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BS2" t="n">
         <v>1775952000</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0.3048</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>14.992076</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>97910</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>97910</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>157767</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>121976</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>121976</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1892000000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1918000000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>73</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>111.525</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.68037903</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>88.173</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>92.53413</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.02151199</v>
-      </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="BU2" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>129</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>124.1375</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>124.375</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>strong_buy</t>
+        </is>
+      </c>
+      <c r="CB2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>194765952</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>9.738</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>183478480</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>61157496</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.931</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>2780802816</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>11.478</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>139.04</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0.10795</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>259953280</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>69959736</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>138080096</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>0.09347999999999999</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.06598</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>0.07761</v>
+      </c>
+      <c r="CV2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="AY2" t="b">
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>1833.SR</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="DB2" t="b">
         <v>0</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>1758391552</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>10.213225</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0.057789996</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>9195000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.52927</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.007979999999999999</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>26.641</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.5509176</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1798675200</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1774915200</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>160711232</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>4:3</t>
-        </is>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1770768000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>9.584</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>-0.08599031</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.27449715</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1775952000</v>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="BY2" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>129</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>114.2</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>122.9875</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>124.375</v>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CE2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>194765952</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>9.738</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>183478480</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>61157496</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.341</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.931</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>2780802816</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>11.478</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>139.04</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>0.10795</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.34076</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>259953280</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>69959736</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>138080096</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>0.09347999999999999</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>0.06598</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>0.07761</v>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>1833.SR</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="DE2" t="b">
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>1781784859</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>finmb_1819703702</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>Asia/Riyadh</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>sr_market</t>
+        </is>
+      </c>
+      <c r="DM2" t="b">
         <v>0</v>
       </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>Almawarid Manpower Company</t>
+        </is>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1687158000000</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.40000153</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>101.0 - 103.4</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>Saudi</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>179872</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>28.599998</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.3917808</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>73.0 - 111.525</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>-9.925003</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.08899353</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1.8546343</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>9</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>11.288889</v>
+      </c>
+      <c r="ED2" t="inlineStr">
         <is>
           <t>Al Mawarid Manpower Co.</t>
         </is>
       </c>
-      <c r="DH2" t="b">
+      <c r="EE2" t="n">
+        <v>9.945</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0.10850472</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>8.722374</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0.09391254</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>1.3 - Strong Buy</t>
+        </is>
+      </c>
+      <c r="EL2" t="b">
         <v>0</v>
       </c>
-      <c r="DI2" t="n">
-        <v>1687158000000</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-1.300003</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>94.35 - 96.0</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Saudi</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>157767</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>21.599998</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.2958904</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>73.0 - 111.525</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-16.925003</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.15175971</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-8.599031</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>8.055</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>Almawarid Manpower Company</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>1780402785</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>SAU</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>finmb_1819703702</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>Asia/Riyadh</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>10800000</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>sr_market</t>
-        </is>
-      </c>
-      <c r="EE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>11.744258</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>6.427002</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.07289082</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>2.0658722</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>0.022325518</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>15</v>
-      </c>
       <c r="EM2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EO2" t="n">
-        <v>-1.3555819</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="EQ2" t="inlineStr"/>
+        <v>-0.3921584</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="EO2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
